--- a/B&I-With formuals Modified 28 Jan 2025.xlsx
+++ b/B&I-With formuals Modified 28 Jan 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude\SalariesSummary\Sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Claude\SalariesSummary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36F1C34-B39E-47C3-84F1-98A277AF08ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9E9F6F-36C4-4A88-850B-EB0C60E120DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Partial 1-2" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="177">
   <si>
     <t>#</t>
   </si>
@@ -447,6 +447,129 @@
   </si>
   <si>
     <t>أ/خالد محمد حلمى</t>
+  </si>
+  <si>
+    <t>أ/ إيهاب حمدى إبراهيم امام</t>
+  </si>
+  <si>
+    <t>ا / اميره شــريف</t>
+  </si>
+  <si>
+    <t>د/هانى صلاح الدين محمد سري الدين</t>
+  </si>
+  <si>
+    <t>أ/ أحمد سعيد أحمد محمد علي</t>
+  </si>
+  <si>
+    <t>أ/ عبدالرحمن أحمد عبدالعزيز حسن</t>
+  </si>
+  <si>
+    <t>أ/أحمد سيف الدين أبو بكر سري الدين</t>
+  </si>
+  <si>
+    <t>أ/احمد ابو العباس محمد الاتربي</t>
+  </si>
+  <si>
+    <t>أ/حبيبة محمود سمير محمود عيسى</t>
+  </si>
+  <si>
+    <t>أ/عبد الله عمرو حافظ</t>
+  </si>
+  <si>
+    <t>أ/كريم ايمن محمد عادل</t>
+  </si>
+  <si>
+    <t>أ/ليلي امين محمد امين طموم</t>
+  </si>
+  <si>
+    <t>أ/محمد حمدى كامل</t>
+  </si>
+  <si>
+    <t>أ/محمد عبد العزيز عبدالحافظ</t>
+  </si>
+  <si>
+    <t>أ/منة الله البلتاجى</t>
+  </si>
+  <si>
+    <t>أ/ناجى رمضان أمين محمد</t>
+  </si>
+  <si>
+    <t>أ/نهى عمرو محمد رضوان</t>
+  </si>
+  <si>
+    <t>أ/هاني أحمد الدالي</t>
+  </si>
+  <si>
+    <t>أ/ أحمد محمد رزق</t>
+  </si>
+  <si>
+    <t>أ/ أحمد محمد عبدالسلام</t>
+  </si>
+  <si>
+    <t>أ/ إيمان صبحى شكرى</t>
+  </si>
+  <si>
+    <t>أ/ محمود على محمود حسين</t>
+  </si>
+  <si>
+    <t>أ/ مروة شريف عبدالحميد سلامة</t>
+  </si>
+  <si>
+    <t>أ/ نيرمين عصمت محمد حجازي</t>
+  </si>
+  <si>
+    <t>أ/أحمد سمير حسن السيد</t>
+  </si>
+  <si>
+    <t>أ/حازم ابراهيم عبد الحميد محمد فتاتة</t>
+  </si>
+  <si>
+    <t>أ/دعاء عبد الدايم إبراهيم نصار</t>
+  </si>
+  <si>
+    <t>أ/سامي ابراهيم محمد</t>
+  </si>
+  <si>
+    <t>أ/شريف شكرى محمد</t>
+  </si>
+  <si>
+    <t>أ/طارق محمد جمعه</t>
+  </si>
+  <si>
+    <t>أ/عاصم محمد سعيد عبده</t>
+  </si>
+  <si>
+    <t>أ/عمرو عبد الكريم صقر</t>
+  </si>
+  <si>
+    <t>أ/محمد حسن محمد كامل</t>
+  </si>
+  <si>
+    <t>أ/محمد عبدالجواد محمد</t>
+  </si>
+  <si>
+    <t>أ/مختار احمد المجدلي</t>
+  </si>
+  <si>
+    <t>أ/منه الله محب عبدالغفار السيد</t>
+  </si>
+  <si>
+    <t>أ/ محمد فاروق عبد الحليم</t>
+  </si>
+  <si>
+    <t>أ/هالة فوزي</t>
+  </si>
+  <si>
+    <t>د/أمجد سعيد</t>
+  </si>
+  <si>
+    <t>د/أمينة العطيفي</t>
+  </si>
+  <si>
+    <t>د/وليد رزق</t>
+  </si>
+  <si>
+    <t>د/ أحمد بغدادي رشدي محمد</t>
   </si>
 </sst>
 </file>
@@ -1828,18 +1951,42 @@
     <xf numFmtId="43" fontId="4" fillId="20" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1847,30 +1994,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2537,12 +2660,12 @@
       <c r="T5" s="43"/>
     </row>
     <row r="6" spans="1:20" s="1" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A6" s="173" t="s">
+      <c r="A6" s="160" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="174"/>
-      <c r="C6" s="174"/>
-      <c r="D6" s="174"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="161"/>
       <c r="E6" s="63">
         <f t="shared" ref="E6:I6" si="2">SUM(E3:E5)</f>
         <v>440000</v>
@@ -5132,11 +5255,11 @@
       <c r="T48" s="45"/>
     </row>
     <row r="49" spans="1:20" s="1" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A49" s="164" t="s">
+      <c r="A49" s="172" t="s">
         <v>95</v>
       </c>
-      <c r="B49" s="165"/>
-      <c r="C49" s="165"/>
+      <c r="B49" s="173"/>
+      <c r="C49" s="173"/>
       <c r="D49" s="33"/>
       <c r="E49" s="71">
         <f>SUM(E48,E42,E21,E6)</f>
@@ -5186,11 +5309,11 @@
       <c r="T49" s="46"/>
     </row>
     <row r="50" spans="1:20" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A50" s="164" t="s">
+      <c r="A50" s="172" t="s">
         <v>97</v>
       </c>
-      <c r="B50" s="165"/>
-      <c r="C50" s="165"/>
+      <c r="B50" s="173"/>
+      <c r="C50" s="173"/>
       <c r="D50" s="33"/>
       <c r="E50" s="71">
         <f>SUM(E42,E21,E6)</f>
@@ -5241,10 +5364,10 @@
     </row>
     <row r="52" spans="1:20" ht="35.1" customHeight="1" thickBot="1"/>
     <row r="53" spans="1:20" s="1" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A53" s="167" t="s">
+      <c r="A53" s="164" t="s">
         <v>96</v>
       </c>
-      <c r="B53" s="168"/>
+      <c r="B53" s="165"/>
       <c r="C53" s="83" t="s">
         <v>4</v>
       </c>
@@ -5275,8 +5398,8 @@
       <c r="T53"/>
     </row>
     <row r="54" spans="1:20" s="1" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A54" s="169"/>
-      <c r="B54" s="170"/>
+      <c r="A54" s="166"/>
+      <c r="B54" s="167"/>
       <c r="C54" s="87">
         <f>E49</f>
         <v>1292119</v>
@@ -5309,18 +5432,18 @@
       <c r="T54"/>
     </row>
     <row r="55" spans="1:20" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A55" s="171"/>
-      <c r="B55" s="172"/>
-      <c r="C55" s="166">
+      <c r="A55" s="168"/>
+      <c r="B55" s="169"/>
+      <c r="C55" s="174">
         <f t="shared" ref="C55:E55" si="23">IFERROR(((D54-C54)/C54),0)</f>
         <v>0.30970909026181026</v>
       </c>
-      <c r="D55" s="161"/>
-      <c r="E55" s="166">
+      <c r="D55" s="171"/>
+      <c r="E55" s="174">
         <f t="shared" si="23"/>
         <v>0.27022554000944815</v>
       </c>
-      <c r="F55" s="161"/>
+      <c r="F55" s="171"/>
       <c r="G55" s="50">
         <f>IFERROR(((#REF!-G54)/G54),0)</f>
         <v>0</v>
@@ -5328,10 +5451,10 @@
     </row>
     <row r="56" spans="1:20" ht="35.1" customHeight="1" thickBot="1"/>
     <row r="57" spans="1:20" ht="35.1" customHeight="1">
-      <c r="A57" s="167" t="s">
+      <c r="A57" s="164" t="s">
         <v>98</v>
       </c>
-      <c r="B57" s="168"/>
+      <c r="B57" s="165"/>
       <c r="C57" s="83" t="s">
         <v>4</v>
       </c>
@@ -5349,8 +5472,8 @@
       </c>
     </row>
     <row r="58" spans="1:20" ht="35.1" customHeight="1">
-      <c r="A58" s="169"/>
-      <c r="B58" s="170"/>
+      <c r="A58" s="166"/>
+      <c r="B58" s="167"/>
       <c r="C58" s="87">
         <f>E50</f>
         <v>1162119</v>
@@ -5370,18 +5493,18 @@
       <c r="G58" s="35"/>
     </row>
     <row r="59" spans="1:20" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A59" s="171"/>
-      <c r="B59" s="172"/>
-      <c r="C59" s="160">
+      <c r="A59" s="168"/>
+      <c r="B59" s="169"/>
+      <c r="C59" s="170">
         <f t="shared" ref="C59" si="24">IFERROR(((D58-C58)/C58),0)</f>
         <v>0.32284215299810087</v>
       </c>
-      <c r="D59" s="161"/>
-      <c r="E59" s="160">
+      <c r="D59" s="171"/>
+      <c r="E59" s="170">
         <f t="shared" ref="E59" si="25">IFERROR(((F58-E58)/E58),0)</f>
         <v>0.2771547737620943</v>
       </c>
-      <c r="F59" s="161"/>
+      <c r="F59" s="171"/>
       <c r="G59" s="51">
         <f>IFERROR(((#REF!-G58)/G58),0)</f>
         <v>0</v>
@@ -5389,11 +5512,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A57:B59"/>
-    <mergeCell ref="C59:D59"/>
     <mergeCell ref="E59:F59"/>
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="A49:C49"/>
@@ -5401,6 +5519,11 @@
     <mergeCell ref="E55:F55"/>
     <mergeCell ref="A53:B55"/>
     <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A57:B59"/>
+    <mergeCell ref="C59:D59"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="50" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
@@ -5536,7 +5659,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>18</v>
@@ -5618,7 +5741,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="C4" s="54" t="s">
         <v>21</v>
@@ -5704,7 +5827,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>100</v>
@@ -5786,12 +5909,12 @@
       <c r="Y5" s="77"/>
     </row>
     <row r="6" spans="1:25" s="1" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A6" s="173" t="s">
+      <c r="A6" s="160" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="174"/>
-      <c r="C6" s="174"/>
-      <c r="D6" s="174"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="161"/>
       <c r="E6" s="63">
         <f t="shared" ref="E6:I6" si="7">SUM(E3:E5)</f>
         <v>440000</v>
@@ -5858,7 +5981,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>24</v>
@@ -5944,7 +6067,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>26</v>
@@ -6030,7 +6153,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>28</v>
@@ -6118,7 +6241,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>30</v>
+        <v>151</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>28</v>
@@ -6204,7 +6327,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>24</v>
@@ -6290,7 +6413,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>33</v>
@@ -6376,7 +6499,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>34</v>
+        <v>141</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>35</v>
@@ -6462,7 +6585,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>24</v>
@@ -6548,7 +6671,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>38</v>
@@ -6634,7 +6757,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>33</v>
@@ -6720,7 +6843,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>38</v>
@@ -6806,7 +6929,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>38</v>
@@ -6892,7 +7015,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>42</v>
+        <v>145</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>38</v>
@@ -6980,7 +7103,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="C20" s="23" t="s">
         <v>26</v>
@@ -7132,7 +7255,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>45</v>
+        <v>161</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>46</v>
@@ -7306,7 +7429,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>49</v>
+        <v>153</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>50</v>
@@ -7392,7 +7515,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>51</v>
+        <v>158</v>
       </c>
       <c r="C25" s="15" t="s">
         <v>52</v>
@@ -7478,7 +7601,7 @@
         <v>5</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>54</v>
@@ -7564,7 +7687,7 @@
         <v>6</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>55</v>
+        <v>159</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>56</v>
@@ -7650,7 +7773,7 @@
         <v>7</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>57</v>
+        <v>155</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>58</v>
@@ -7736,7 +7859,7 @@
         <v>8</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>60</v>
@@ -7822,7 +7945,7 @@
         <v>9</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="C30" s="15" t="s">
         <v>62</v>
@@ -7908,7 +8031,7 @@
         <v>10</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>63</v>
+        <v>162</v>
       </c>
       <c r="C31" s="15" t="s">
         <v>64</v>
@@ -7994,7 +8117,7 @@
         <v>11</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="C32" s="15" t="s">
         <v>66</v>
@@ -8080,7 +8203,7 @@
         <v>12</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>67</v>
+        <v>166</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>68</v>
@@ -8166,7 +8289,7 @@
         <v>13</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>70</v>
@@ -8252,7 +8375,7 @@
         <v>14</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>71</v>
+        <v>164</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>72</v>
@@ -8338,7 +8461,7 @@
         <v>15</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>72</v>
@@ -8424,7 +8547,7 @@
         <v>16</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>74</v>
+        <v>171</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>75</v>
@@ -8510,7 +8633,7 @@
         <v>17</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>77</v>
@@ -8596,7 +8719,7 @@
         <v>18</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>78</v>
+        <v>170</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>79</v>
@@ -8682,7 +8805,7 @@
         <v>19</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>56</v>
@@ -8768,7 +8891,7 @@
         <v>20</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>82</v>
@@ -8924,7 +9047,7 @@
         <v>1</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>84</v>
+        <v>172</v>
       </c>
       <c r="C43" s="28" t="s">
         <v>85</v>
@@ -9008,7 +9131,7 @@
         <v>2</v>
       </c>
       <c r="B44" s="30" t="s">
-        <v>87</v>
+        <v>174</v>
       </c>
       <c r="C44" s="31" t="s">
         <v>88</v>
@@ -9088,7 +9211,7 @@
         <v>3</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>90</v>
+        <v>173</v>
       </c>
       <c r="C45" s="31" t="s">
         <v>88</v>
@@ -9168,7 +9291,7 @@
         <v>4</v>
       </c>
       <c r="B46" s="30" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
       <c r="C46" s="31" t="s">
         <v>88</v>
@@ -9248,7 +9371,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="30" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="C47" s="31" t="s">
         <v>93</v>
@@ -9390,11 +9513,11 @@
       <c r="Y48" s="110"/>
     </row>
     <row r="49" spans="1:25" s="1" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A49" s="164" t="s">
+      <c r="A49" s="172" t="s">
         <v>95</v>
       </c>
-      <c r="B49" s="165"/>
-      <c r="C49" s="165"/>
+      <c r="B49" s="173"/>
+      <c r="C49" s="173"/>
       <c r="D49" s="33"/>
       <c r="E49" s="71">
         <f>SUM(E48,E42,E21,E6)</f>
@@ -9458,11 +9581,11 @@
       <c r="Y49" s="112"/>
     </row>
     <row r="50" spans="1:25" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A50" s="164" t="s">
+      <c r="A50" s="172" t="s">
         <v>97</v>
       </c>
-      <c r="B50" s="165"/>
-      <c r="C50" s="165"/>
+      <c r="B50" s="173"/>
+      <c r="C50" s="173"/>
       <c r="D50" s="33"/>
       <c r="E50" s="71">
         <f>SUM(E42,E21,E6)</f>
@@ -9527,10 +9650,10 @@
     </row>
     <row r="52" spans="1:25" ht="35.1" customHeight="1" thickBot="1"/>
     <row r="53" spans="1:25" s="1" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A53" s="167" t="s">
+      <c r="A53" s="164" t="s">
         <v>96</v>
       </c>
-      <c r="B53" s="168"/>
+      <c r="B53" s="165"/>
       <c r="C53" s="83" t="s">
         <v>4</v>
       </c>
@@ -9566,8 +9689,8 @@
       <c r="Y53" s="74"/>
     </row>
     <row r="54" spans="1:25" s="1" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A54" s="169"/>
-      <c r="B54" s="170"/>
+      <c r="A54" s="166"/>
+      <c r="B54" s="167"/>
       <c r="C54" s="87">
         <f>E49</f>
         <v>1268119</v>
@@ -9605,18 +9728,18 @@
       <c r="Y54" s="74"/>
     </row>
     <row r="55" spans="1:25" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A55" s="171"/>
-      <c r="B55" s="172"/>
-      <c r="C55" s="166">
+      <c r="A55" s="168"/>
+      <c r="B55" s="169"/>
+      <c r="C55" s="174">
         <f t="shared" ref="C55:E55" si="46">IFERROR(((D54-C54)/C54),0)</f>
         <v>0.33449621052913803</v>
       </c>
-      <c r="D55" s="161"/>
-      <c r="E55" s="166">
+      <c r="D55" s="171"/>
+      <c r="E55" s="174">
         <f t="shared" si="46"/>
         <v>0.28521980475779085</v>
       </c>
-      <c r="F55" s="161"/>
+      <c r="F55" s="171"/>
       <c r="G55" s="50">
         <f>IFERROR(((#REF!-G54)/G54),0)</f>
         <v>0</v>
@@ -9624,10 +9747,10 @@
     </row>
     <row r="56" spans="1:25" ht="35.1" customHeight="1" thickBot="1"/>
     <row r="57" spans="1:25" ht="35.1" customHeight="1">
-      <c r="A57" s="167" t="s">
+      <c r="A57" s="164" t="s">
         <v>98</v>
       </c>
-      <c r="B57" s="168"/>
+      <c r="B57" s="165"/>
       <c r="C57" s="83" t="s">
         <v>4</v>
       </c>
@@ -9645,8 +9768,8 @@
       </c>
     </row>
     <row r="58" spans="1:25" ht="35.1" customHeight="1">
-      <c r="A58" s="169"/>
-      <c r="B58" s="170"/>
+      <c r="A58" s="166"/>
+      <c r="B58" s="167"/>
       <c r="C58" s="87">
         <f>E50</f>
         <v>1138119</v>
@@ -9666,18 +9789,18 @@
       <c r="G58" s="108"/>
     </row>
     <row r="59" spans="1:25" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A59" s="171"/>
-      <c r="B59" s="172"/>
-      <c r="C59" s="160">
+      <c r="A59" s="168"/>
+      <c r="B59" s="169"/>
+      <c r="C59" s="170">
         <f t="shared" ref="C59" si="47">IFERROR(((D58-C58)/C58),0)</f>
         <v>0.35073748878632199</v>
       </c>
-      <c r="D59" s="161"/>
-      <c r="E59" s="160">
+      <c r="D59" s="171"/>
+      <c r="E59" s="170">
         <f t="shared" ref="E59" si="48">IFERROR(((F58-E58)/E58),0)</f>
         <v>0.29340593279669908</v>
       </c>
-      <c r="F59" s="161"/>
+      <c r="F59" s="171"/>
       <c r="G59" s="51">
         <f>IFERROR(((#REF!-G58)/G58),0)</f>
         <v>0</v>
@@ -9685,18 +9808,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A53:B55"/>
     <mergeCell ref="C55:D55"/>
     <mergeCell ref="E55:F55"/>
     <mergeCell ref="A57:B59"/>
     <mergeCell ref="C59:D59"/>
     <mergeCell ref="E59:F59"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="50" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
@@ -10205,12 +10328,12 @@
       <c r="Y5" s="77"/>
     </row>
     <row r="6" spans="1:25" s="1" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A6" s="173" t="s">
+      <c r="A6" s="160" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="174"/>
-      <c r="C6" s="174"/>
-      <c r="D6" s="174"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="161"/>
       <c r="E6" s="63">
         <f t="shared" ref="E6:I6" si="7">SUM(E3:E5)</f>
         <v>440000</v>
@@ -13812,11 +13935,11 @@
       <c r="Y48" s="110"/>
     </row>
     <row r="49" spans="1:25" s="1" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A49" s="164" t="s">
+      <c r="A49" s="172" t="s">
         <v>95</v>
       </c>
-      <c r="B49" s="165"/>
-      <c r="C49" s="165"/>
+      <c r="B49" s="173"/>
+      <c r="C49" s="173"/>
       <c r="D49" s="33"/>
       <c r="E49" s="71">
         <f>SUM(E48,E42,E21,E6)</f>
@@ -13880,11 +14003,11 @@
       <c r="Y49" s="112"/>
     </row>
     <row r="50" spans="1:25" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A50" s="164" t="s">
+      <c r="A50" s="172" t="s">
         <v>97</v>
       </c>
-      <c r="B50" s="165"/>
-      <c r="C50" s="165"/>
+      <c r="B50" s="173"/>
+      <c r="C50" s="173"/>
       <c r="D50" s="33"/>
       <c r="E50" s="71">
         <f>SUM(E42,E21,E6)</f>
@@ -13949,10 +14072,10 @@
     </row>
     <row r="52" spans="1:25" ht="35.1" customHeight="1" thickBot="1"/>
     <row r="53" spans="1:25" s="1" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A53" s="167" t="s">
+      <c r="A53" s="164" t="s">
         <v>96</v>
       </c>
-      <c r="B53" s="168"/>
+      <c r="B53" s="165"/>
       <c r="C53" s="83" t="s">
         <v>4</v>
       </c>
@@ -13988,8 +14111,8 @@
       <c r="Y53" s="74"/>
     </row>
     <row r="54" spans="1:25" s="1" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A54" s="169"/>
-      <c r="B54" s="170"/>
+      <c r="A54" s="166"/>
+      <c r="B54" s="167"/>
       <c r="C54" s="87">
         <f>E49</f>
         <v>1268119</v>
@@ -14027,18 +14150,18 @@
       <c r="Y54" s="74"/>
     </row>
     <row r="55" spans="1:25" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A55" s="171"/>
-      <c r="B55" s="172"/>
-      <c r="C55" s="166">
+      <c r="A55" s="168"/>
+      <c r="B55" s="169"/>
+      <c r="C55" s="174">
         <f t="shared" ref="C55:E55" si="46">IFERROR(((D54-C54)/C54),0)</f>
         <v>0.33449621052913803</v>
       </c>
-      <c r="D55" s="161"/>
-      <c r="E55" s="166">
+      <c r="D55" s="171"/>
+      <c r="E55" s="174">
         <f t="shared" si="46"/>
         <v>0.28521980475779085</v>
       </c>
-      <c r="F55" s="161"/>
+      <c r="F55" s="171"/>
       <c r="G55" s="50">
         <f>IFERROR(((#REF!-G54)/G54),0)</f>
         <v>0</v>
@@ -14046,10 +14169,10 @@
     </row>
     <row r="56" spans="1:25" ht="35.1" customHeight="1" thickBot="1"/>
     <row r="57" spans="1:25" ht="35.1" customHeight="1">
-      <c r="A57" s="167" t="s">
+      <c r="A57" s="164" t="s">
         <v>98</v>
       </c>
-      <c r="B57" s="168"/>
+      <c r="B57" s="165"/>
       <c r="C57" s="83" t="s">
         <v>4</v>
       </c>
@@ -14067,8 +14190,8 @@
       </c>
     </row>
     <row r="58" spans="1:25" ht="35.1" customHeight="1">
-      <c r="A58" s="169"/>
-      <c r="B58" s="170"/>
+      <c r="A58" s="166"/>
+      <c r="B58" s="167"/>
       <c r="C58" s="87">
         <f>E50</f>
         <v>1138119</v>
@@ -14088,18 +14211,18 @@
       <c r="G58" s="108"/>
     </row>
     <row r="59" spans="1:25" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A59" s="171"/>
-      <c r="B59" s="172"/>
-      <c r="C59" s="160">
+      <c r="A59" s="168"/>
+      <c r="B59" s="169"/>
+      <c r="C59" s="170">
         <f t="shared" ref="C59" si="47">IFERROR(((D58-C58)/C58),0)</f>
         <v>0.35073748878632199</v>
       </c>
-      <c r="D59" s="161"/>
-      <c r="E59" s="160">
+      <c r="D59" s="171"/>
+      <c r="E59" s="170">
         <f t="shared" ref="E59" si="48">IFERROR(((F58-E58)/E58),0)</f>
         <v>0.29340593279669908</v>
       </c>
-      <c r="F59" s="161"/>
+      <c r="F59" s="171"/>
       <c r="G59" s="51">
         <f>IFERROR(((#REF!-G58)/G58),0)</f>
         <v>0</v>
@@ -14107,18 +14230,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A53:B55"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="A57:B59"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:F59"/>
     <mergeCell ref="A50:C50"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A48:C48"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A53:B55"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="A57:B59"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:F59"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="37" fitToHeight="0" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
